--- a/healthcare_surveys/014_ivf_cost_assessment_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/014_ivf_cost_assessment_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1217,8 +1217,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medicare'}</t>
+          <t>medicare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medicare'}</t>
+          <t>Medicare</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'medicaid'}</t>
+          <t>medicaid</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Medicaid'}</t>
+          <t>Medicaid</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'tricare'}</t>
+          <t>tricare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Tricare'}</t>
+          <t>Tricare</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'in_vitro_fertilization_(ivf)'}</t>
+          <t>in_vitro_fertilization_(ivf)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'In Vitro Fertilization (IVF)'}</t>
+          <t>In Vitro Fertilization (IVF)</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'intrauterine_insemination_(iui)'}</t>
+          <t>intrauterine_insemination_(iui)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Intrauterine Insemination (IUI)'}</t>
+          <t>Intrauterine Insemination (IUI)</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'intrauterine_insemination_(iui)_with_icsi'}</t>
+          <t>intrauterine_insemination_(iui)_with_icsi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Intrauterine Insemination (IUI) with ICSI'}</t>
+          <t>Intrauterine Insemination (IUI) with ICSI</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'ivf'}</t>
+          <t>ivf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'IVF'}</t>
+          <t>IVF</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'iui'}</t>
+          <t>iui</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'IUI'}</t>
+          <t>IUI</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'icsi'}</t>
+          <t>icsi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'ICSI'}</t>
+          <t>ICSI</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full_coverage'}</t>
+          <t>full_coverage</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Full Coverage'}</t>
+          <t>Full Coverage</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'partial_coverage'}</t>
+          <t>partial_coverage</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Partial Coverage'}</t>
+          <t>Partial Coverage</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'no_coverage'}</t>
+          <t>no_coverage</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'No Coverage'}</t>
+          <t>No Coverage</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'frozen_embryo_transfer_(fet)'}</t>
+          <t>frozen_embryo_transfer_(fet)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Frozen Embryo Transfer (FET)'}</t>
+          <t>Frozen Embryo Transfer (FET)</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'intracytoplasmic_sperm_injection_(icsi)'}</t>
+          <t>intracytoplasmic_sperm_injection_(icsi)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Intracytoplasmic Sperm Injection (ICSI)'}</t>
+          <t>Intracytoplasmic Sperm Injection (ICSI)</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'donor_egg'}</t>
+          <t>donor_egg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Donor Egg'}</t>
+          <t>Donor Egg</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'surrogacy'}</t>
+          <t>surrogacy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Surrogacy'}</t>
+          <t>Surrogacy</t>
         </is>
       </c>
     </row>
